--- a/artfynd/A 39237-2022 artfynd.xlsx
+++ b/artfynd/A 39237-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39237-2022 artfynd.xlsx
+++ b/artfynd/A 39237-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103306907</v>
+        <v>103306906</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616722.5563543306</v>
+        <v>616717</v>
       </c>
       <c r="R2" t="n">
-        <v>7222296.936207736</v>
+        <v>7222250</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,62 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115413209</v>
+        <v>103306907</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lankasjön, Ly lm</t>
+          <t>Estbergskojan, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616765</v>
+        <v>616723</v>
       </c>
       <c r="R3" t="n">
-        <v>7222233</v>
+        <v>7222297</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:14</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:14</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,15 +861,135 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115413209</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lankasjön, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>616765</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7222233</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
